--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008450004899078973</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>23282316</v>
+        <v>4367392</v>
       </c>
       <c r="L2" t="n">
-        <v>13496887</v>
+        <v>2327944</v>
       </c>
       <c r="M2" t="n">
-        <v>3321511</v>
+        <v>542084</v>
       </c>
       <c r="N2" t="n">
-        <v>107760</v>
+        <v>14298</v>
       </c>
       <c r="O2" t="n">
-        <v>1973146</v>
+        <v>336285</v>
       </c>
       <c r="P2" t="n">
-        <v>685496</v>
+        <v>120537</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.905783474445343</v>
+        <v>0.847201943397522</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8207696080207825</v>
+        <v>0.710166871547699</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7716874480247498</v>
+        <v>0.6278611421585083</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2880975306034088</v>
+        <v>0.1965036690235138</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7905444502830505</v>
+        <v>0.6755125522613525</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9034591317176819</v>
+        <v>0.808056652545929</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026420486158906</v>
       </c>
       <c r="C3" t="n">
-        <v>1810</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>23282316</v>
+        <v>4367392</v>
       </c>
       <c r="E3" t="n">
-        <v>1833350</v>
+        <v>637254</v>
       </c>
       <c r="F3" t="n">
-        <v>22093</v>
+        <v>11126</v>
       </c>
       <c r="G3" t="n">
-        <v>1954</v>
+        <v>806</v>
       </c>
       <c r="H3" t="n">
-        <v>1005</v>
+        <v>628</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>50081185</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>54083713</v>
+        <v>10524341</v>
       </c>
       <c r="L3" t="n">
-        <v>62379526</v>
+        <v>12106093</v>
       </c>
       <c r="M3" t="n">
-        <v>76003997</v>
+        <v>15074883</v>
       </c>
       <c r="N3" t="n">
-        <v>80936073</v>
+        <v>16181878</v>
       </c>
       <c r="O3" t="n">
-        <v>78579347</v>
+        <v>15658511</v>
       </c>
       <c r="P3" t="n">
-        <v>80608165</v>
+        <v>16107575</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9260128736495972</v>
+        <v>0.8704192042350769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8269555568695068</v>
+        <v>0.7111641764640808</v>
       </c>
       <c r="T3" t="n">
-        <v>0.712572455406189</v>
+        <v>0.5807510018348694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2418057322502136</v>
+        <v>0.1601873189210892</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7750391960144043</v>
+        <v>0.6599620580673218</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7091937065124512</v>
+        <v>0.6232748627662659</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2269873</v>
+        <v>744970</v>
       </c>
       <c r="E4" t="n">
-        <v>13496887</v>
+        <v>2327944</v>
       </c>
       <c r="F4" t="n">
-        <v>510539</v>
+        <v>177995</v>
       </c>
       <c r="G4" t="n">
-        <v>13404</v>
+        <v>6250</v>
       </c>
       <c r="H4" t="n">
-        <v>28723</v>
+        <v>15239</v>
       </c>
       <c r="I4" t="n">
-        <v>1750</v>
+        <v>1029</v>
       </c>
       <c r="J4" t="n">
-        <v>1925</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>2421747</v>
+        <v>787686</v>
       </c>
       <c r="L4" t="n">
-        <v>2947298</v>
+        <v>950080</v>
       </c>
       <c r="M4" t="n">
-        <v>982707</v>
+        <v>321298</v>
       </c>
       <c r="N4" t="n">
-        <v>266280</v>
+        <v>58464</v>
       </c>
       <c r="O4" t="n">
-        <v>522787</v>
+        <v>161537</v>
       </c>
       <c r="P4" t="n">
-        <v>73250</v>
+        <v>28632</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9157864451408386</v>
+        <v>0.858653724193573</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8238509893417358</v>
+        <v>0.7106651663780212</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7409527897834778</v>
+        <v>0.6033878922462463</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2629296183586121</v>
+        <v>0.1764967143535614</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7827149629592896</v>
+        <v>0.6676467657089233</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7946255207061768</v>
+        <v>0.7037383317947388</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>96282</v>
+        <v>27693</v>
       </c>
       <c r="E5" t="n">
-        <v>973688</v>
+        <v>269547</v>
       </c>
       <c r="F5" t="n">
-        <v>3321511</v>
+        <v>542084</v>
       </c>
       <c r="G5" t="n">
-        <v>72279</v>
+        <v>19052</v>
       </c>
       <c r="H5" t="n">
-        <v>186984</v>
+        <v>69601</v>
       </c>
       <c r="I5" t="n">
-        <v>10552</v>
+        <v>5442</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1860224</v>
+        <v>650181</v>
       </c>
       <c r="L5" t="n">
-        <v>2824289</v>
+        <v>945483</v>
       </c>
       <c r="M5" t="n">
-        <v>1339785</v>
+        <v>391335</v>
       </c>
       <c r="N5" t="n">
-        <v>337887</v>
+        <v>74960</v>
       </c>
       <c r="O5" t="n">
-        <v>572720</v>
+        <v>173267</v>
       </c>
       <c r="P5" t="n">
-        <v>281089</v>
+        <v>72856</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9475557208061218</v>
+        <v>0.9119471907615662</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9293113350868225</v>
+        <v>0.8839185833930969</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9715548157691956</v>
+        <v>0.9563594460487366</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9926003217697144</v>
+        <v>0.9918293356895447</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9865825772285461</v>
+        <v>0.9794971346855164</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9956601858139038</v>
+        <v>0.99378502368927</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>54867</v>
+        <v>14602</v>
       </c>
       <c r="E6" t="n">
-        <v>95367</v>
+        <v>19230</v>
       </c>
       <c r="F6" t="n">
-        <v>143756</v>
+        <v>29605</v>
       </c>
       <c r="G6" t="n">
-        <v>107760</v>
+        <v>14298</v>
       </c>
       <c r="H6" t="n">
-        <v>42097</v>
+        <v>10731</v>
       </c>
       <c r="I6" t="n">
-        <v>1698</v>
+        <v>771</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>369</v>
       </c>
       <c r="E7" t="n">
-        <v>42789</v>
+        <v>22913</v>
       </c>
       <c r="F7" t="n">
-        <v>296979</v>
+        <v>97992</v>
       </c>
       <c r="G7" t="n">
-        <v>173190</v>
+        <v>30608</v>
       </c>
       <c r="H7" t="n">
-        <v>1973146</v>
+        <v>336285</v>
       </c>
       <c r="I7" t="n">
-        <v>59238</v>
+        <v>21385</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>2104</v>
+        <v>1136</v>
       </c>
       <c r="F8" t="n">
-        <v>9340</v>
+        <v>4580</v>
       </c>
       <c r="G8" t="n">
-        <v>5453</v>
+        <v>1748</v>
       </c>
       <c r="H8" t="n">
-        <v>263978</v>
+        <v>65338</v>
       </c>
       <c r="I8" t="n">
-        <v>685496</v>
+        <v>120537</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
